--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2018/ARKANSAS_2018.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2018/ARKANSAS_2018.xlsx
@@ -2616,7 +2616,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C126">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C217">
@@ -10158,7 +10158,7 @@
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C545">
